--- a/tabtools/qa/baseline/workbooks/regtab_compact_multi.xlsx
+++ b/tabtools/qa/baseline/workbooks/regtab_compact_multi.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="63" uniqueCount="26">
   <si>
     <t>Refactor Baseline: regtab compact</t>
   </si>
@@ -97,7 +97,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="286">
+  <fonts count="328">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -269,615 +269,736 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1173,6 +1294,30 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10"/>
       <b/>
       <name val="Arial"/>
@@ -1234,6 +1379,28 @@
     </font>
     <font>
       <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1330,8 +1497,20 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="63">
+  <fills count="74">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1643,8 +1822,63 @@
         <fgColor rgb="FFDBE5F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="218">
+  <borders count="248">
     <border>
       <left/>
       <right/>
@@ -1997,147 +2231,210 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -2200,14 +2497,14 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
       <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -2228,7 +2525,28 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -2284,14 +2602,7 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
@@ -2299,160 +2610,6 @@
     <border>
       <left style="none"/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
       <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -2508,140 +2665,126 @@
     </border>
     <border>
       <left style="thin"/>
-      <right style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
       <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="thin"/>
       <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
@@ -2649,20 +2792,216 @@
     <border>
       <left style="none"/>
       <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
@@ -2670,6 +3009,20 @@
     <border>
       <left style="none"/>
       <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -2704,6 +3057,13 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -2746,6 +3106,13 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -2788,6 +3155,13 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -2830,6 +3204,13 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -2872,6 +3253,13 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -2914,203 +3302,259 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
       <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
@@ -3133,7 +3577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -3255,7 +3699,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3278,707 +3722,827 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="4" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="64" fillId="4" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="5" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="6" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="7" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="8" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="9" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="10" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="11" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="12" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="65" fillId="5" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="6" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="7" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="8" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="9" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="11" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="14" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="13" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="75" fillId="15" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="14" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="76" fillId="16" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="15" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="77" fillId="17" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="16" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="78" fillId="18" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="17" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="79" fillId="19" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="20" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="81" fillId="21" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="19" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="82" fillId="22" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="20" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="83" fillId="23" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="21" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="84" fillId="24" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="22" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="85" fillId="25" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="23" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="87" fillId="26" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="24" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="89" fillId="27" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="25" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="91" fillId="28" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="26" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="93" fillId="29" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="27" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="28" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="95" fillId="30" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="31" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="32" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="33" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="29" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="100" fillId="34" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="30" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="31" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="32" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="101" fillId="35" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="36" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="37" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="38" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="33" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="105" fillId="39" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="34" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="35" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="36" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="106" fillId="40" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="41" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="42" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="43" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="37" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="110" fillId="44" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="38" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="111" fillId="45" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="39" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="112" fillId="46" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="100" fillId="40" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="113" fillId="47" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="41" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="114" fillId="48" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="42" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="115" fillId="49" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="43" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="116" fillId="50" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="44" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="117" fillId="51" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="45" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="46" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="118" fillId="52" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="47" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="48" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="119" fillId="53" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="49" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="50" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="120" fillId="54" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="55" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="51" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="52" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="56" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="57" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="58" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="59" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="60" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="61" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="53" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="54" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="62" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="63" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="55" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="179" fillId="64" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="163" fillId="56" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="57" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="58" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="181" fillId="65" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="66" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="67" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="68" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="171" fillId="59" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="191" fillId="69" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="173" fillId="60" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="193" fillId="70" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="175" fillId="61" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="195" fillId="71" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="177" fillId="62" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="197" fillId="72" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="189" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="191" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="193" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="197" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="199" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="201" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="203" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="205" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="209" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="213" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="219" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="199" fillId="73" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="221" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="227" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="247" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="253" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="257" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="259" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="263" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="265" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="269" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="271" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="273" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="275" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="277" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="317" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="279" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="281" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="283" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="285" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3991,202 +4555,229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="13.7109375" style="3" customWidth="true"/>
-    <col min="3" max="3" width="23.14453125" style="4" customWidth="true"/>
-    <col min="5" max="5" width="23.14453125" style="5" customWidth="true"/>
-    <col min="4" max="4" width="11.3203125" style="6" customWidth="true"/>
-    <col min="6" max="6" width="11.3203125" style="7" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="3" customWidth="true"/>
+    <col min="3" max="3" width="27.2109375" style="4" customWidth="true"/>
+    <col min="5" max="5" width="27.2109375" style="5" customWidth="true"/>
+    <col min="4" max="4" width="7.7109375" style="6" customWidth="true"/>
+    <col min="6" max="6" width="7.7109375" style="7" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="211" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="212" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="190" t="s">
+      <c r="C1" s="213" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="191" t="s">
+      <c r="D1" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="192" t="s">
+      <c r="E1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="193" t="s">
+      <c r="F1" s="216" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="217" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="142" t="s">
+      <c r="C2" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="143" t="s">
+      <c r="D2" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="144" t="s">
+      <c r="E2" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="145" t="s">
+      <c r="F2" s="160" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="161" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="147" t="s">
+      <c r="B3" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="148" t="s">
+      <c r="C3" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="149" t="s">
+      <c r="D3" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="150" t="s">
+      <c r="E3" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="151" t="s">
+      <c r="F3" s="167" t="s">
         <v>13</v>
+      </c>
+      <c r="G3" s="168" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="153" t="s">
+      <c r="B4" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="195" t="s">
+      <c r="D4" s="219" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="196" t="s">
+      <c r="E4" s="220" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="197" t="s">
+      <c r="F4" s="221" t="s">
         <v>23</v>
+      </c>
+      <c r="G4" s="222" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="159" t="s">
+      <c r="B5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="198" t="s">
+      <c r="C5" s="223" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="199" t="s">
+      <c r="D5" s="224" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="200" t="s">
+      <c r="E5" s="225" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="201" t="s">
+      <c r="F5" s="226" t="s">
         <v>24</v>
+      </c>
+      <c r="G5" s="227" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="164" t="s">
+      <c r="A6" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="165" t="s">
+      <c r="B6" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="202" t="s">
+      <c r="C6" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="203" t="s">
+      <c r="D6" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="204" t="s">
+      <c r="E6" s="230" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="205" t="s">
+      <c r="F6" s="231" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="232" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="170" t="s">
+      <c r="A7" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="171" t="s">
+      <c r="B7" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="206" t="s">
+      <c r="C7" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="207" t="s">
+      <c r="D7" s="234" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="208" t="s">
+      <c r="E7" s="235" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="209" t="s">
+      <c r="F7" s="236" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="237" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="176" t="s">
+      <c r="A8" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="177" t="s">
+      <c r="B8" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="210" t="s">
+      <c r="C8" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="211" t="s">
+      <c r="D8" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="212" t="s">
+      <c r="E8" s="240" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="213" t="s">
+      <c r="F8" s="241" t="s">
         <v>24</v>
+      </c>
+      <c r="G8" s="242" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="182" t="s">
+      <c r="A9" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="183" t="s">
+      <c r="B9" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="214" t="s">
+      <c r="C9" s="243" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="215" t="s">
+      <c r="D9" s="244" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="216" t="s">
+      <c r="E9" s="245" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="217" t="s">
+      <c r="F9" s="246" t="s">
         <v>25</v>
+      </c>
+      <c r="G9" s="247" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
 </worksheet>
 </file>